--- a/Problem14_Executive_Decision_Support_Dashboard/reports/financial_impact_reporting_packaging/AMEX_Problem14_Executive_Financial_Impact_Workbook.xlsx
+++ b/Problem14_Executive_Decision_Support_Dashboard/reports/financial_impact_reporting_packaging/AMEX_Problem14_Executive_Financial_Impact_Workbook.xlsx
@@ -25,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="9">
@@ -133,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +168,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -707,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -717,6 +724,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -728,6 +736,13 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Platform-Wide Financial Rollup, Problems 1-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
         </is>
       </c>
     </row>
